--- a/excel/3xlsx/item.xlsx
+++ b/excel/3xlsx/item.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -446,8 +446,9 @@
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -478,10 +479,15 @@
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>堆叠上限</t>
+          <t>占格宽</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>占格高</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>排序权重</t>
         </is>
@@ -515,10 +521,15 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>maxStack</t>
+          <t>width</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>height</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>sortPriority</t>
         </is>
@@ -560,6 +571,11 @@
           <t>int</t>
         </is>
       </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -593,6 +609,11 @@
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>all</t>
         </is>
@@ -606,6 +627,7 @@
       <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -615,6 +637,7 @@
       <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -639,9 +662,12 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
         <v>100</v>
       </c>
     </row>
@@ -668,9 +694,12 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
         <v>110</v>
       </c>
     </row>
@@ -697,9 +726,12 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
         <v>90</v>
       </c>
     </row>
@@ -729,6 +761,9 @@
         <v>1</v>
       </c>
       <c r="G10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" t="n">
         <v>520</v>
       </c>
     </row>
@@ -755,9 +790,12 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="n">
         <v>510</v>
       </c>
     </row>
@@ -784,9 +822,12 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
         <v>60</v>
       </c>
     </row>
@@ -813,9 +854,12 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>999</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
         <v>50</v>
       </c>
     </row>
@@ -842,9 +886,12 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="n">
         <v>800</v>
       </c>
     </row>
@@ -871,9 +918,12 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>999999</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
         <v>10</v>
       </c>
     </row>

--- a/excel/3xlsx/item.xlsx
+++ b/excel/3xlsx/item.xlsx
@@ -438,17 +438,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -489,6 +490,11 @@
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
+          <t>形状掩码</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
           <t>排序权重</t>
         </is>
       </c>
@@ -531,6 +537,11 @@
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
+          <t>shape</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
           <t>sortPriority</t>
         </is>
       </c>
@@ -573,6 +584,11 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
           <t>int</t>
         </is>
       </c>
@@ -614,6 +630,11 @@
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>all</t>
         </is>
@@ -628,6 +649,7 @@
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -638,6 +660,7 @@
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="n"/>
       <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -667,7 +690,8 @@
       <c r="G7" t="n">
         <v>1</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="n">
         <v>100</v>
       </c>
     </row>
@@ -699,7 +723,8 @@
       <c r="G8" t="n">
         <v>2</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="n">
         <v>110</v>
       </c>
     </row>
@@ -731,7 +756,8 @@
       <c r="G9" t="n">
         <v>1</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="n">
         <v>90</v>
       </c>
     </row>
@@ -763,7 +789,8 @@
       <c r="G10" t="n">
         <v>3</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="n">
         <v>520</v>
       </c>
     </row>
@@ -795,7 +822,8 @@
       <c r="G11" t="n">
         <v>2</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="n">
         <v>510</v>
       </c>
     </row>
@@ -827,7 +855,8 @@
       <c r="G12" t="n">
         <v>1</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="n">
         <v>60</v>
       </c>
     </row>
@@ -859,7 +888,8 @@
       <c r="G13" t="n">
         <v>1</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="n">
         <v>50</v>
       </c>
     </row>
@@ -874,7 +904,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>主线任务道具，不可丢弃。</t>
+          <t>L 形主线道具,不可丢弃。</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -891,39 +921,82 @@
       <c r="G14" t="n">
         <v>2</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>10|11</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>800</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
+        <v>4002</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>曲柄扳手</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>T 形工具,占 5 格。</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>UI/Item/wrench</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>111|010</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
         <v>5001</v>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>金币</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>通用货币。</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D16" t="n">
         <v>5</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>UI/Item/coin</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" t="n">
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="n">
         <v>10</v>
       </c>
     </row>

--- a/excel/3xlsx/item.xlsx
+++ b/excel/3xlsx/item.xlsx
@@ -438,18 +438,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -495,6 +496,11 @@
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
+          <t>叠加上限</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
           <t>排序权重</t>
         </is>
       </c>
@@ -542,6 +548,11 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
+          <t>maxStack</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
           <t>sortPriority</t>
         </is>
       </c>
@@ -592,6 +603,11 @@
           <t>int</t>
         </is>
       </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -635,6 +651,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>all</t>
         </is>
@@ -650,6 +671,7 @@
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="2" t="n"/>
       <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -661,6 +683,7 @@
       <c r="G6" s="2" t="n"/>
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -692,6 +715,9 @@
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
+        <v>20</v>
+      </c>
+      <c r="J7" t="n">
         <v>100</v>
       </c>
     </row>
@@ -725,6 +751,9 @@
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
+        <v>10</v>
+      </c>
+      <c r="J8" t="n">
         <v>110</v>
       </c>
     </row>
@@ -758,6 +787,9 @@
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
+        <v>20</v>
+      </c>
+      <c r="J9" t="n">
         <v>90</v>
       </c>
     </row>
@@ -791,6 +823,9 @@
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
         <v>520</v>
       </c>
     </row>
@@ -824,6 +859,9 @@
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
         <v>510</v>
       </c>
     </row>
@@ -857,6 +895,9 @@
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
+        <v>50</v>
+      </c>
+      <c r="J12" t="n">
         <v>60</v>
       </c>
     </row>
@@ -892,6 +933,9 @@
       <c r="I13" t="n">
         <v>50</v>
       </c>
+      <c r="J13" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -927,6 +971,9 @@
         </is>
       </c>
       <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
         <v>800</v>
       </c>
     </row>
@@ -964,6 +1011,9 @@
         </is>
       </c>
       <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
         <v>70</v>
       </c>
     </row>
@@ -997,6 +1047,9 @@
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
+        <v>999</v>
+      </c>
+      <c r="J16" t="n">
         <v>10</v>
       </c>
     </row>

--- a/excel/3xlsx/item.xlsx
+++ b/excel/3xlsx/item.xlsx
@@ -438,19 +438,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -476,30 +478,40 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
+          <t>品质</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
           <t>图标路径</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>占格宽</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>占格高</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>形状掩码</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>叠加上限</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>预估价值</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>排序权重</t>
         </is>
@@ -528,30 +540,40 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
+          <t>quality</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
           <t>iconPath</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>width</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>height</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>shape</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>maxStack</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
         <is>
           <t>sortPriority</t>
         </is>
@@ -580,30 +602,40 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>uint</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
@@ -632,30 +664,40 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>client</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>all</t>
         </is>
@@ -672,6 +714,8 @@
       <c r="H5" s="2" t="n"/>
       <c r="I5" s="2" t="n"/>
       <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="n"/>
+      <c r="L5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -684,6 +728,8 @@
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
       <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -702,22 +748,28 @@
       <c r="D7" t="n">
         <v>1</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>UI/Item/potion_hp_s</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="n">
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="n">
         <v>20</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
+        <v>15</v>
+      </c>
+      <c r="L7" t="n">
         <v>100</v>
       </c>
     </row>
@@ -738,22 +790,28 @@
       <c r="D8" t="n">
         <v>1</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>UI/Item/potion_hp_l</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
       <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
         <v>2</v>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="n">
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="n">
         <v>10</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
+        <v>40</v>
+      </c>
+      <c r="L8" t="n">
         <v>110</v>
       </c>
     </row>
@@ -774,22 +832,28 @@
       <c r="D9" t="n">
         <v>1</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>UI/Item/energy_drink</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="n">
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="n">
         <v>20</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
+        <v>25</v>
+      </c>
+      <c r="L9" t="n">
         <v>90</v>
       </c>
     </row>
@@ -810,22 +874,28 @@
       <c r="D10" t="n">
         <v>2</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>UI/Item/sword_iron</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
       <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
         <v>3</v>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="n">
-        <v>1</v>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>120</v>
+      </c>
+      <c r="L10" t="n">
         <v>520</v>
       </c>
     </row>
@@ -846,22 +916,28 @@
       <c r="D11" t="n">
         <v>2</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>UI/Item/armor_iron</t>
         </is>
-      </c>
-      <c r="F11" t="n">
-        <v>2</v>
       </c>
       <c r="G11" t="n">
         <v>2</v>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="n">
-        <v>1</v>
-      </c>
+      <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>200</v>
+      </c>
+      <c r="L11" t="n">
         <v>510</v>
       </c>
     </row>
@@ -882,22 +958,28 @@
       <c r="D12" t="n">
         <v>3</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>UI/Item/ore_iron</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="n">
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="n">
         <v>50</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L12" t="n">
         <v>60</v>
       </c>
     </row>
@@ -918,22 +1000,28 @@
       <c r="D13" t="n">
         <v>3</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>UI/Item/wood</t>
         </is>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>2</v>
       </c>
-      <c r="G13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="n">
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="n">
         <v>50</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
+        <v>5</v>
+      </c>
+      <c r="L13" t="n">
         <v>50</v>
       </c>
     </row>
@@ -954,26 +1042,32 @@
       <c r="D14" t="n">
         <v>4</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>UI/Item/relic</t>
         </is>
-      </c>
-      <c r="F14" t="n">
-        <v>2</v>
       </c>
       <c r="G14" t="n">
         <v>2</v>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>10|11</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>1</v>
-      </c>
       <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>800</v>
       </c>
     </row>
@@ -994,26 +1088,32 @@
       <c r="D15" t="n">
         <v>3</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>UI/Item/wrench</t>
         </is>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>3</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>2</v>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>111|010</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>1</v>
-      </c>
       <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>90</v>
+      </c>
+      <c r="L15" t="n">
         <v>70</v>
       </c>
     </row>
@@ -1034,22 +1134,28 @@
       <c r="D16" t="n">
         <v>5</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>UI/Item/coin</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="n">
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="n">
         <v>999</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
         <v>10</v>
       </c>
     </row>
